--- a/exp_now.xlsx
+++ b/exp_now.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="414">
   <si>
     <t>'26년 20주차 시험용 주간 계획 (2026-05-18~2026-05-23)_V1.0  [PC/LTR]</t>
   </si>
@@ -1340,6 +1340,64 @@
   <si>
     <t>SRFM Width 50mm
 [HEW)OP Inform]</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>245/45ZR20Y XL</t>
+  </si>
+  <si>
+    <t>RE/DM H101</t>
+  </si>
+  <si>
+    <t>DR75395</t>
+  </si>
+  <si>
+    <t>DN69338</t>
+  </si>
+  <si>
+    <t>FY24753</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>FS00822</t>
+  </si>
+  <si>
+    <t>FHB0439</t>
+  </si>
+  <si>
+    <t>FX30138</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>CE09N12</t>
+  </si>
+  <si>
+    <t>GU29459</t>
+  </si>
+  <si>
+    <t>26856</t>
+  </si>
+  <si>
+    <t>05/23 토</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>[정규용] 26856</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aramid JLB</t>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1004</t>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
 </sst>
@@ -1552,7 +1610,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1649,6 +1707,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1677,7 +1741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1871,6 +1935,12 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2179,7 +2249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CL23"/>
+  <dimension ref="A1:CL24"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" outlineLevelCol="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -7977,6 +8047,261 @@
         <v>135</v>
       </c>
     </row>
+    <row r="24" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2026041079</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="11">
+        <v>1039046</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24" s="12">
+        <v>4</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="O24" s="13">
+        <v>0</v>
+      </c>
+      <c r="P24" s="13">
+        <v>14</v>
+      </c>
+      <c r="Q24" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="R24" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="S24" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="T24" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="U24" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="V24" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="W24" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="X24" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="Y24" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="Z24" s="16">
+        <v>266</v>
+      </c>
+      <c r="AA24" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB24" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC24" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="AD24" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE24" s="17">
+        <v>115</v>
+      </c>
+      <c r="AF24" s="17">
+        <v>594</v>
+      </c>
+      <c r="AG24" s="17">
+        <v>2120</v>
+      </c>
+      <c r="AH24" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="AI24" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="AJ24" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="AK24" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="AL24" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="AM24" s="17">
+        <v>620</v>
+      </c>
+      <c r="AN24" s="17">
+        <v>90</v>
+      </c>
+      <c r="AO24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AQ24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AS24" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="AT24" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU24" s="17">
+        <v>225</v>
+      </c>
+      <c r="AV24" s="17">
+        <v>30</v>
+      </c>
+      <c r="AW24" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="AX24" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY24" s="17">
+        <v>215</v>
+      </c>
+      <c r="AZ24" s="17">
+        <v>30</v>
+      </c>
+      <c r="BA24" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB24" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="BC24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="BE24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="BF24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="BG24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH24" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI24" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="BJ24" s="17"/>
+      <c r="BK24" s="17"/>
+      <c r="BL24" s="17">
+        <v>20</v>
+      </c>
+      <c r="BM24" s="67" t="s">
+        <v>411</v>
+      </c>
+      <c r="BN24" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO24" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="BP24" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="BQ24" s="15"/>
+      <c r="BR24" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="BS24" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="BT24" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="BU24" s="20">
+        <v>1622</v>
+      </c>
+      <c r="BV24" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="BW24" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="BX24" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="BY24" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="BZ24" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="CA24" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="CB24" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="CC24" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="CD24" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="CE24" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="CF24" s="15"/>
+      <c r="CG24" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="CH24" s="15"/>
+      <c r="CI24" s="15"/>
+      <c r="CJ24" s="15"/>
+      <c r="CK24" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="26" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/exp_now.xlsx
+++ b/exp_now.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="DP_요일별" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -591,9 +591,6 @@
   </si>
   <si>
     <t>205/45R17W XL</t>
-  </si>
-  <si>
-    <t>06/09 화</t>
   </si>
   <si>
     <t>RE/DS H145</t>
@@ -1084,19 +1081,19 @@
   </si>
   <si>
     <t>225/45ZR18Y XL</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>김상훈</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>김노연</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>김한유</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1114,11 +1111,11 @@
       <t>22847 22848
 (수리중)</t>
     </r>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>혜원</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1136,36 +1133,40 @@
       <t>24U02 24U03
 (개조중)</t>
     </r>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>DR75490</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>RE/DS H175</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>RE/DS H136</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>[신제품 개발] 26854 26855</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>DN69902 정규 Die
 Mold 1조 입고</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>RE/DS H162</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>RE/DS H186</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>06/11 목</t>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1316,14 +1317,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FFFF6600"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
       <color rgb="FF008000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -1343,6 +1336,14 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF00FF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1554,22 +1555,22 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2290,7 +2291,7 @@
         <v>92</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>93</v>
@@ -2335,7 +2336,7 @@
         <v>101</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="S3" s="16" t="s">
         <v>102</v>
@@ -2549,7 +2550,7 @@
         <v>92</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>93</v>
@@ -2564,7 +2565,7 @@
         <v>1035591</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>96</v>
@@ -2594,7 +2595,7 @@
         <v>101</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="S4" s="16" t="s">
         <v>102</v>
@@ -2805,10 +2806,10 @@
         <v>91</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>93</v>
@@ -2823,7 +2824,7 @@
         <v>1039078</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>147</v>
@@ -2853,7 +2854,7 @@
         <v>101</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="S5" s="16" t="s">
         <v>102</v>
@@ -2871,7 +2872,7 @@
         <v>106</v>
       </c>
       <c r="X5" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Y5" s="11" t="s">
         <v>150</v>
@@ -2886,7 +2887,7 @@
         <v>110</v>
       </c>
       <c r="AC5" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD5" s="26" t="s">
         <v>112</v>
@@ -2901,7 +2902,7 @@
         <v>1925</v>
       </c>
       <c r="AH5" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AI5" s="19">
         <v>360</v>
@@ -2910,7 +2911,7 @@
         <v>325</v>
       </c>
       <c r="AK5" s="19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL5" s="19" t="s">
         <v>140</v>
@@ -2922,19 +2923,19 @@
         <v>90</v>
       </c>
       <c r="AO5" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AP5" s="19" t="s">
         <v>140</v>
       </c>
       <c r="AQ5" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AR5" s="19" t="s">
         <v>156</v>
       </c>
       <c r="AS5" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AT5" s="19" t="s">
         <v>142</v>
@@ -2946,7 +2947,7 @@
         <v>27</v>
       </c>
       <c r="AW5" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AX5" s="19" t="s">
         <v>142</v>
@@ -2990,23 +2991,23 @@
         <v>19</v>
       </c>
       <c r="BM5" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BN5" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="BO5" s="17" t="s">
         <v>199</v>
-      </c>
-      <c r="BO5" s="17" t="s">
-        <v>200</v>
       </c>
       <c r="BP5" s="17" t="s">
         <v>125</v>
       </c>
       <c r="BQ5" s="16"/>
       <c r="BR5" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="BS5" s="22" t="s">
         <v>201</v>
-      </c>
-      <c r="BS5" s="22" t="s">
-        <v>202</v>
       </c>
       <c r="BT5" s="22" t="s">
         <v>128</v>
@@ -3019,32 +3020,32 @@
         <v>165</v>
       </c>
       <c r="BX5" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="BY5" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ5" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="CA5" s="16" t="s">
         <v>203</v>
-      </c>
-      <c r="BY5" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="BZ5" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="CA5" s="16" t="s">
-        <v>204</v>
       </c>
       <c r="CB5" s="16" t="s">
         <v>125</v>
       </c>
       <c r="CC5" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="CD5" s="16" t="s">
         <v>168</v>
       </c>
       <c r="CE5" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="CF5" s="16"/>
       <c r="CG5" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="CH5" s="16"/>
       <c r="CI5" s="16"/>
@@ -3058,10 +3059,10 @@
         <v>91</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>145</v>
@@ -3076,10 +3077,10 @@
         <v>1039091</v>
       </c>
       <c r="H6" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="I6" s="31" t="s">
         <v>207</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>208</v>
       </c>
       <c r="J6" s="31">
         <v>4</v>
@@ -3106,28 +3107,28 @@
         <v>101</v>
       </c>
       <c r="R6" s="34" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S6" s="35" t="s">
         <v>102</v>
       </c>
       <c r="T6" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="U6" s="36" t="s">
         <v>211</v>
-      </c>
-      <c r="U6" s="36" t="s">
-        <v>212</v>
       </c>
       <c r="V6" s="36" t="s">
         <v>105</v>
       </c>
       <c r="W6" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="X6" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="X6" s="37" t="s">
+      <c r="Y6" s="37" t="s">
         <v>214</v>
-      </c>
-      <c r="Y6" s="37" t="s">
-        <v>215</v>
       </c>
       <c r="Z6" s="36">
         <v>256</v>
@@ -3139,7 +3140,7 @@
         <v>110</v>
       </c>
       <c r="AC6" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AD6" s="38" t="s">
         <v>150</v>
@@ -3154,7 +3155,7 @@
         <v>2200</v>
       </c>
       <c r="AH6" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AI6" s="37">
         <v>460</v>
@@ -3163,10 +3164,10 @@
         <v>425</v>
       </c>
       <c r="AK6" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL6" s="37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM6" s="37">
         <v>590</v>
@@ -3175,22 +3176,22 @@
         <v>90</v>
       </c>
       <c r="AO6" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="AP6" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ6" s="37" t="s">
         <v>219</v>
-      </c>
-      <c r="AP6" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="AQ6" s="37" t="s">
-        <v>220</v>
       </c>
       <c r="AR6" s="37" t="s">
         <v>156</v>
       </c>
       <c r="AS6" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="AT6" s="37" t="s">
         <v>221</v>
-      </c>
-      <c r="AT6" s="37" t="s">
-        <v>222</v>
       </c>
       <c r="AU6" s="37">
         <v>215</v>
@@ -3199,10 +3200,10 @@
         <v>27</v>
       </c>
       <c r="AW6" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AX6" s="37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AY6" s="37">
         <v>205</v>
@@ -3243,26 +3244,26 @@
         <v>20</v>
       </c>
       <c r="BM6" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="BN6" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="BN6" s="37" t="s">
+      <c r="BO6" s="36" t="s">
         <v>225</v>
-      </c>
-      <c r="BO6" s="36" t="s">
-        <v>226</v>
       </c>
       <c r="BP6" s="36" t="s">
         <v>125</v>
       </c>
       <c r="BQ6" s="35"/>
       <c r="BR6" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="BS6" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="BS6" s="39" t="s">
+      <c r="BT6" s="39" t="s">
         <v>228</v>
-      </c>
-      <c r="BT6" s="39" t="s">
-        <v>229</v>
       </c>
       <c r="BU6" s="39">
         <v>1626</v>
@@ -3272,16 +3273,16 @@
         <v>130</v>
       </c>
       <c r="BX6" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="BY6" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ6" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="CA6" s="35" t="s">
         <v>230</v>
-      </c>
-      <c r="BY6" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="BZ6" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="CA6" s="35" t="s">
-        <v>231</v>
       </c>
       <c r="CB6" s="35" t="s">
         <v>125</v>
@@ -3293,16 +3294,16 @@
         <v>135</v>
       </c>
       <c r="CE6" s="35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CF6" s="35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CG6" s="35" t="s">
         <v>136</v>
       </c>
       <c r="CH6" s="35" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="CI6" s="35"/>
       <c r="CJ6" s="35"/>
@@ -3315,31 +3316,31 @@
         <v>91</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>93</v>
       </c>
       <c r="E7" s="8">
-        <v>2026050836</v>
+        <v>2026043356</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="G7" s="10">
-        <v>2020515</v>
+        <v>1039077</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="J7" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>97</v>
@@ -3347,47 +3348,47 @@
       <c r="L7" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="M7" s="43" t="s">
-        <v>240</v>
+      <c r="M7" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>241</v>
+        <v>100</v>
       </c>
       <c r="O7" s="13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P7" s="13">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="41" t="s">
-        <v>173</v>
+        <v>12</v>
+      </c>
+      <c r="Q7" s="45" t="s">
+        <v>208</v>
       </c>
       <c r="R7" s="15" t="s">
         <v>338</v>
       </c>
       <c r="S7" s="16" t="s">
-        <v>242</v>
+        <v>102</v>
       </c>
       <c r="T7" s="17" t="s">
-        <v>243</v>
+        <v>103</v>
       </c>
       <c r="U7" s="17" t="s">
-        <v>244</v>
+        <v>104</v>
       </c>
       <c r="V7" s="17" t="s">
         <v>105</v>
       </c>
       <c r="W7" s="17" t="s">
-        <v>245</v>
+        <v>106</v>
       </c>
       <c r="X7" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y7" s="19" t="s">
-        <v>247</v>
+        <v>271</v>
+      </c>
+      <c r="Y7" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="Z7" s="17">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="AA7" s="17" t="s">
         <v>109</v>
@@ -3396,79 +3397,79 @@
         <v>110</v>
       </c>
       <c r="AC7" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="AD7" s="19" t="s">
-        <v>249</v>
+        <v>272</v>
+      </c>
+      <c r="AD7" s="11" t="s">
+        <v>150</v>
       </c>
       <c r="AE7" s="19">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="AF7" s="19">
-        <v>760</v>
+        <v>560</v>
       </c>
       <c r="AG7" s="19">
-        <v>1980</v>
+        <v>1925</v>
       </c>
       <c r="AH7" s="19" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="AI7" s="19">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AJ7" s="19">
-        <v>440</v>
+        <v>365</v>
       </c>
       <c r="AK7" s="19" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="AL7" s="19" t="s">
         <v>115</v>
       </c>
       <c r="AM7" s="19">
-        <v>620</v>
+        <v>580</v>
       </c>
       <c r="AN7" s="19">
         <v>90</v>
       </c>
       <c r="AO7" s="19" t="s">
-        <v>252</v>
+        <v>99</v>
       </c>
       <c r="AP7" s="19" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="AQ7" s="19" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="AR7" s="19" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="AS7" s="19" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="AT7" s="19" t="s">
-        <v>254</v>
+        <v>142</v>
       </c>
       <c r="AU7" s="19">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="AV7" s="19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AW7" s="19" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="AX7" s="19" t="s">
-        <v>254</v>
+        <v>142</v>
       </c>
       <c r="AY7" s="19">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="AZ7" s="19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BA7" s="19" t="s">
-        <v>159</v>
+        <v>277</v>
       </c>
       <c r="BB7" s="19" t="s">
         <v>99</v>
@@ -3489,56 +3490,56 @@
         <v>99</v>
       </c>
       <c r="BH7" s="19" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="BI7" s="19" t="s">
-        <v>256</v>
+        <v>99</v>
       </c>
       <c r="BJ7" s="19"/>
       <c r="BK7" s="19"/>
       <c r="BL7" s="19">
-        <v>15</v>
-      </c>
-      <c r="BM7" s="19" t="s">
-        <v>257</v>
+        <v>19</v>
+      </c>
+      <c r="BM7" s="11" t="s">
+        <v>278</v>
       </c>
       <c r="BN7" s="19" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="BO7" s="17" t="s">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="BP7" s="17" t="s">
         <v>125</v>
       </c>
       <c r="BQ7" s="16"/>
       <c r="BR7" s="22" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="BS7" s="22" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="BT7" s="22" t="s">
-        <v>262</v>
+        <v>128</v>
       </c>
       <c r="BU7" s="22">
-        <v>1208</v>
+        <v>1542</v>
       </c>
       <c r="BV7" s="16"/>
       <c r="BW7" s="16" t="s">
-        <v>263</v>
+        <v>165</v>
       </c>
       <c r="BX7" s="23" t="s">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="BY7" s="16" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="BZ7" s="16" t="s">
         <v>99</v>
       </c>
       <c r="CA7" s="16" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="CB7" s="16" t="s">
         <v>125</v>
@@ -3547,20 +3548,16 @@
         <v>134</v>
       </c>
       <c r="CD7" s="16" t="s">
-        <v>266</v>
+        <v>168</v>
       </c>
       <c r="CE7" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="CF7" s="16" t="s">
-        <v>267</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="CF7" s="16"/>
       <c r="CG7" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="CH7" s="16" t="s">
-        <v>269</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="CH7" s="16"/>
       <c r="CI7" s="16"/>
       <c r="CJ7" s="16"/>
       <c r="CK7" s="16" t="s">
@@ -3568,257 +3565,257 @@
       </c>
     </row>
     <row r="8" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2026051548</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="G8" s="10">
-        <v>1039070</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="I8" s="12" t="s">
+      <c r="B8" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>331</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="27">
+        <v>2026052106</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="30">
+        <v>1039065</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="31">
         <v>4</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="M8" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="N8" s="13" t="s">
+      <c r="M8" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="N8" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="32">
         <v>0</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="32">
         <v>10</v>
       </c>
-      <c r="Q8" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="R8" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="S8" s="16" t="s">
+      <c r="Q8" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="R8" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="S8" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="T8" s="17" t="s">
+      <c r="T8" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="U8" s="17" t="s">
+      <c r="U8" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="V8" s="17" t="s">
+      <c r="V8" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="W8" s="17" t="s">
+      <c r="W8" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="X8" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="Y8" s="11" t="s">
+      <c r="X8" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y8" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="Z8" s="17">
-        <v>220</v>
-      </c>
-      <c r="AA8" s="17" t="s">
+      <c r="Z8" s="36">
+        <v>286</v>
+      </c>
+      <c r="AA8" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="AB8" s="17" t="s">
+      <c r="AB8" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="AC8" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="AD8" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE8" s="19">
-        <v>100</v>
-      </c>
-      <c r="AF8" s="19">
-        <v>490</v>
-      </c>
-      <c r="AG8" s="19">
-        <v>1780</v>
-      </c>
-      <c r="AH8" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI8" s="19">
+      <c r="AC8" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD8" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="AE8" s="37">
+        <v>120</v>
+      </c>
+      <c r="AF8" s="37">
+        <v>636</v>
+      </c>
+      <c r="AG8" s="37">
+        <v>2040</v>
+      </c>
+      <c r="AH8" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="AI8" s="37">
+        <v>440</v>
+      </c>
+      <c r="AJ8" s="37">
+        <v>405</v>
+      </c>
+      <c r="AK8" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL8" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="AM8" s="37">
+        <v>550</v>
+      </c>
+      <c r="AN8" s="37">
+        <v>90</v>
+      </c>
+      <c r="AO8" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="AP8" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ8" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="AR8" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS8" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="AT8" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="AU8" s="37">
+        <v>245</v>
+      </c>
+      <c r="AV8" s="37">
+        <v>27</v>
+      </c>
+      <c r="AW8" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="AX8" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="AY8" s="37">
+        <v>235</v>
+      </c>
+      <c r="AZ8" s="37">
+        <v>27</v>
+      </c>
+      <c r="BA8" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="BB8" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC8" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD8" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE8" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="BF8" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG8" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="BH8" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="BI8" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ8" s="37"/>
+      <c r="BK8" s="37"/>
+      <c r="BL8" s="37">
+        <v>19</v>
+      </c>
+      <c r="BM8" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="BN8" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="BO8" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="BP8" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="BQ8" s="35"/>
+      <c r="BR8" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS8" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="BT8" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="BU8" s="39">
+        <v>1546</v>
+      </c>
+      <c r="BV8" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="AJ8" s="19">
-        <v>305</v>
-      </c>
-      <c r="AK8" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL8" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="AM8" s="19">
-        <v>430</v>
-      </c>
-      <c r="AN8" s="19">
-        <v>90</v>
-      </c>
-      <c r="AO8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="AP8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="AQ8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="AR8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="AS8" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="AT8" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="AU8" s="19">
-        <v>190</v>
-      </c>
-      <c r="AV8" s="19">
-        <v>27</v>
-      </c>
-      <c r="AW8" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="AX8" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="AY8" s="19">
-        <v>180</v>
-      </c>
-      <c r="AZ8" s="19">
-        <v>27</v>
-      </c>
-      <c r="BA8" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="BB8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="BC8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="BF8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="BG8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH8" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="BI8" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="BJ8" s="19"/>
-      <c r="BK8" s="19"/>
-      <c r="BL8" s="19">
-        <v>17</v>
-      </c>
-      <c r="BM8" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="BN8" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="BO8" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="BP8" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ8" s="16"/>
-      <c r="BR8" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="BS8" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="BT8" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="BU8" s="22">
-        <v>1383</v>
-      </c>
-      <c r="BV8" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="BW8" s="16" t="s">
+      <c r="BW8" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="BX8" s="23" t="s">
+      <c r="BX8" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="BY8" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="BZ8" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="CA8" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="CB8" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC8" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="CD8" s="16" t="s">
+      <c r="BY8" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ8" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="CA8" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="CB8" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="CC8" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD8" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="CE8" s="16" t="s">
+      <c r="CE8" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="CF8" s="16"/>
-      <c r="CG8" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="CH8" s="16"/>
-      <c r="CI8" s="16"/>
-      <c r="CJ8" s="16"/>
-      <c r="CK8" s="16" t="s">
+      <c r="CF8" s="35"/>
+      <c r="CG8" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="CH8" s="35"/>
+      <c r="CI8" s="35"/>
+      <c r="CJ8" s="35"/>
+      <c r="CK8" s="35" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3827,31 +3824,31 @@
         <v>91</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>93</v>
       </c>
       <c r="E9" s="8">
-        <v>2026043356</v>
+        <v>2026050836</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="G9" s="10">
-        <v>1039077</v>
+        <v>2020515</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>147</v>
+        <v>238</v>
       </c>
       <c r="J9" s="12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>97</v>
@@ -3859,47 +3856,47 @@
       <c r="L9" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="M9" s="12" t="s">
-        <v>99</v>
+      <c r="M9" s="42" t="s">
+        <v>239</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="O9" s="13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P9" s="13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q9" s="46" t="s">
-        <v>209</v>
+        <v>343</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="S9" s="16" t="s">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>103</v>
+        <v>242</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>104</v>
+        <v>243</v>
       </c>
       <c r="V9" s="17" t="s">
         <v>105</v>
       </c>
       <c r="W9" s="17" t="s">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="X9" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y9" s="11" t="s">
-        <v>150</v>
+        <v>245</v>
+      </c>
+      <c r="Y9" s="19" t="s">
+        <v>246</v>
       </c>
       <c r="Z9" s="17">
-        <v>272</v>
+        <v>194</v>
       </c>
       <c r="AA9" s="17" t="s">
         <v>109</v>
@@ -3908,79 +3905,79 @@
         <v>110</v>
       </c>
       <c r="AC9" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="AD9" s="11" t="s">
-        <v>150</v>
+        <v>247</v>
+      </c>
+      <c r="AD9" s="19" t="s">
+        <v>248</v>
       </c>
       <c r="AE9" s="19">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="AF9" s="19">
-        <v>560</v>
+        <v>760</v>
       </c>
       <c r="AG9" s="19">
-        <v>1925</v>
+        <v>1980</v>
       </c>
       <c r="AH9" s="19" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="AI9" s="19">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AJ9" s="19">
-        <v>365</v>
+        <v>440</v>
       </c>
       <c r="AK9" s="19" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="AL9" s="19" t="s">
         <v>115</v>
       </c>
       <c r="AM9" s="19">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="AN9" s="19">
         <v>90</v>
       </c>
       <c r="AO9" s="19" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="AP9" s="19" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AQ9" s="19" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="AR9" s="19" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="AS9" s="19" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="AT9" s="19" t="s">
-        <v>142</v>
+        <v>253</v>
       </c>
       <c r="AU9" s="19">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="AV9" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AW9" s="19" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="AX9" s="19" t="s">
-        <v>142</v>
+        <v>253</v>
       </c>
       <c r="AY9" s="19">
-        <v>225</v>
+        <v>140</v>
       </c>
       <c r="AZ9" s="19">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BA9" s="19" t="s">
-        <v>278</v>
+        <v>159</v>
       </c>
       <c r="BB9" s="19" t="s">
         <v>99</v>
@@ -4001,56 +3998,56 @@
         <v>99</v>
       </c>
       <c r="BH9" s="19" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="BI9" s="19" t="s">
-        <v>99</v>
+        <v>255</v>
       </c>
       <c r="BJ9" s="19"/>
       <c r="BK9" s="19"/>
       <c r="BL9" s="19">
-        <v>19</v>
-      </c>
-      <c r="BM9" s="11" t="s">
-        <v>279</v>
+        <v>15</v>
+      </c>
+      <c r="BM9" s="19" t="s">
+        <v>256</v>
       </c>
       <c r="BN9" s="19" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="BO9" s="17" t="s">
-        <v>99</v>
+        <v>258</v>
       </c>
       <c r="BP9" s="17" t="s">
         <v>125</v>
       </c>
       <c r="BQ9" s="16"/>
       <c r="BR9" s="22" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="BS9" s="22" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="BT9" s="22" t="s">
-        <v>128</v>
+        <v>261</v>
       </c>
       <c r="BU9" s="22">
-        <v>1542</v>
+        <v>1208</v>
       </c>
       <c r="BV9" s="16"/>
       <c r="BW9" s="16" t="s">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="BX9" s="23" t="s">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="BY9" s="16" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="BZ9" s="16" t="s">
         <v>99</v>
       </c>
       <c r="CA9" s="16" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="CB9" s="16" t="s">
         <v>125</v>
@@ -4059,16 +4056,20 @@
         <v>134</v>
       </c>
       <c r="CD9" s="16" t="s">
-        <v>168</v>
+        <v>265</v>
       </c>
       <c r="CE9" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="CF9" s="16"/>
+        <v>263</v>
+      </c>
+      <c r="CF9" s="16" t="s">
+        <v>266</v>
+      </c>
       <c r="CG9" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="CH9" s="16"/>
+        <v>267</v>
+      </c>
+      <c r="CH9" s="16" t="s">
+        <v>268</v>
+      </c>
       <c r="CI9" s="16"/>
       <c r="CJ9" s="16"/>
       <c r="CK9" s="16" t="s">
@@ -4076,269 +4077,269 @@
       </c>
     </row>
     <row r="10" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>332</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" s="27">
-        <v>2026052106</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="G10" s="30">
-        <v>1039065</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="I10" s="31" t="s">
+      <c r="B10" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2026051548</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1039070</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="12">
         <v>4</v>
       </c>
-      <c r="K10" s="31" t="s">
+      <c r="K10" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="L10" s="31" t="s">
+      <c r="L10" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="M10" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="N10" s="32" t="s">
+      <c r="M10" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="O10" s="32">
+      <c r="O10" s="13">
         <v>0</v>
       </c>
-      <c r="P10" s="32">
+      <c r="P10" s="13">
         <v>10</v>
       </c>
-      <c r="Q10" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="S10" s="35" t="s">
+      <c r="Q10" s="46" t="s">
+        <v>343</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="S10" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="T10" s="36" t="s">
+      <c r="T10" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="U10" s="36" t="s">
+      <c r="U10" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="V10" s="36" t="s">
+      <c r="V10" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="W10" s="36" t="s">
+      <c r="W10" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="X10" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y10" s="38" t="s">
+      <c r="X10" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y10" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="Z10" s="36">
-        <v>286</v>
-      </c>
-      <c r="AA10" s="36" t="s">
+      <c r="Z10" s="17">
+        <v>220</v>
+      </c>
+      <c r="AA10" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="AB10" s="36" t="s">
+      <c r="AB10" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="AC10" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="AD10" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE10" s="37">
-        <v>120</v>
-      </c>
-      <c r="AF10" s="37">
-        <v>636</v>
-      </c>
-      <c r="AG10" s="37">
-        <v>2040</v>
-      </c>
-      <c r="AH10" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="AI10" s="37">
-        <v>440</v>
-      </c>
-      <c r="AJ10" s="37">
-        <v>405</v>
-      </c>
-      <c r="AK10" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="AL10" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="AM10" s="37">
-        <v>550</v>
-      </c>
-      <c r="AN10" s="37">
+      <c r="AC10" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD10" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE10" s="19">
+        <v>100</v>
+      </c>
+      <c r="AF10" s="19">
+        <v>490</v>
+      </c>
+      <c r="AG10" s="19">
+        <v>1780</v>
+      </c>
+      <c r="AH10" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI10" s="19">
+        <v>340</v>
+      </c>
+      <c r="AJ10" s="19">
+        <v>305</v>
+      </c>
+      <c r="AK10" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL10" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="AM10" s="19">
+        <v>430</v>
+      </c>
+      <c r="AN10" s="19">
         <v>90</v>
       </c>
-      <c r="AO10" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="AP10" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="AQ10" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="AR10" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="AS10" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="AT10" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="AU10" s="37">
-        <v>245</v>
-      </c>
-      <c r="AV10" s="37">
+      <c r="AO10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AS10" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="AT10" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU10" s="19">
+        <v>190</v>
+      </c>
+      <c r="AV10" s="19">
         <v>27</v>
       </c>
-      <c r="AW10" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="AX10" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY10" s="37">
-        <v>235</v>
-      </c>
-      <c r="AZ10" s="37">
+      <c r="AW10" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="AX10" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="AY10" s="19">
+        <v>180</v>
+      </c>
+      <c r="AZ10" s="19">
         <v>27</v>
       </c>
-      <c r="BA10" s="37" t="s">
+      <c r="BA10" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="BB10" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="BC10" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="BD10" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="BE10" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="BF10" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="BG10" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="BH10" s="37" t="s">
+      <c r="BB10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="BC10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="BD10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="BE10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="BF10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="BH10" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="BI10" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="BJ10" s="37"/>
-      <c r="BK10" s="37"/>
-      <c r="BL10" s="37">
-        <v>19</v>
-      </c>
-      <c r="BM10" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="BN10" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="BO10" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="BP10" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="BQ10" s="35"/>
-      <c r="BR10" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="BS10" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="BT10" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="BU10" s="39">
-        <v>1546</v>
-      </c>
-      <c r="BV10" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="BW10" s="35" t="s">
+      <c r="BI10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ10" s="19"/>
+      <c r="BK10" s="19"/>
+      <c r="BL10" s="19">
+        <v>17</v>
+      </c>
+      <c r="BM10" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="BN10" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="BO10" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="BP10" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="BQ10" s="16"/>
+      <c r="BR10" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS10" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="BT10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU10" s="22">
+        <v>1383</v>
+      </c>
+      <c r="BV10" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="BW10" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="BX10" s="40" t="s">
+      <c r="BX10" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="BY10" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="BZ10" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="CA10" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="CB10" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="CC10" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="CD10" s="35" t="s">
+      <c r="BY10" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ10" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="CA10" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="CB10" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="CC10" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="CD10" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="CE10" s="35" t="s">
+      <c r="CE10" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="CF10" s="35"/>
-      <c r="CG10" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="CH10" s="35"/>
-      <c r="CI10" s="35"/>
-      <c r="CJ10" s="35"/>
-      <c r="CK10" s="35" t="s">
+      <c r="CF10" s="16"/>
+      <c r="CG10" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="CH10" s="16"/>
+      <c r="CI10" s="16"/>
+      <c r="CJ10" s="16"/>
+      <c r="CK10" s="16" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="C11" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>93</v>
@@ -4347,16 +4348,16 @@
         <v>2026043081</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G11" s="10">
         <v>1026310</v>
       </c>
       <c r="H11" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>286</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>287</v>
       </c>
       <c r="J11" s="12">
         <v>4</v>
@@ -4379,17 +4380,17 @@
       <c r="P11" s="13">
         <v>30</v>
       </c>
-      <c r="Q11" s="44" t="s">
+      <c r="Q11" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="R11" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="R11" s="15" t="s">
+      <c r="S11" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="S11" s="16" t="s">
+      <c r="T11" s="17" t="s">
         <v>290</v>
-      </c>
-      <c r="T11" s="17" t="s">
-        <v>291</v>
       </c>
       <c r="U11" s="17" t="s">
         <v>104</v>
@@ -4401,7 +4402,7 @@
         <v>106</v>
       </c>
       <c r="X11" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Y11" s="19" t="s">
         <v>108</v>
@@ -4416,7 +4417,7 @@
         <v>110</v>
       </c>
       <c r="AC11" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AD11" s="19" t="s">
         <v>112</v>
@@ -4431,7 +4432,7 @@
         <v>2010</v>
       </c>
       <c r="AH11" s="19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AI11" s="19">
         <v>410</v>
@@ -4440,10 +4441,10 @@
         <v>375</v>
       </c>
       <c r="AK11" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AL11" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM11" s="19">
         <v>520</v>
@@ -4452,22 +4453,22 @@
         <v>90</v>
       </c>
       <c r="AO11" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="AP11" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ11" s="19" t="s">
         <v>296</v>
-      </c>
-      <c r="AP11" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="AQ11" s="19" t="s">
-        <v>297</v>
       </c>
       <c r="AR11" s="19" t="s">
         <v>156</v>
       </c>
       <c r="AS11" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="AT11" s="19" t="s">
         <v>298</v>
-      </c>
-      <c r="AT11" s="19" t="s">
-        <v>299</v>
       </c>
       <c r="AU11" s="19">
         <v>190</v>
@@ -4476,10 +4477,10 @@
         <v>24</v>
       </c>
       <c r="AW11" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AX11" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AY11" s="19">
         <v>180</v>
@@ -4520,38 +4521,38 @@
         <v>18</v>
       </c>
       <c r="BM11" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BN11" s="19" t="s">
         <v>123</v>
       </c>
       <c r="BO11" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="BP11" s="17" t="s">
         <v>125</v>
       </c>
       <c r="BQ11" s="16"/>
       <c r="BR11" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="BS11" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="BS11" s="22" t="s">
+      <c r="BT11" s="22" t="s">
         <v>303</v>
-      </c>
-      <c r="BT11" s="22" t="s">
-        <v>304</v>
       </c>
       <c r="BU11" s="22">
         <v>1466</v>
       </c>
       <c r="BV11" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="BW11" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="BW11" s="16" t="s">
-        <v>306</v>
-      </c>
       <c r="BX11" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BY11" s="16" t="s">
         <v>99</v>
@@ -4560,7 +4561,7 @@
         <v>99</v>
       </c>
       <c r="CA11" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="CB11" s="16" t="s">
         <v>125</v>
@@ -4572,16 +4573,16 @@
         <v>135</v>
       </c>
       <c r="CE11" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="CF11" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="CG11" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="CG11" s="16" t="s">
-        <v>310</v>
-      </c>
       <c r="CH11" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16"/>
@@ -4591,13 +4592,13 @@
     </row>
     <row r="12" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="C12" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>93</v>
@@ -4606,16 +4607,16 @@
         <v>2026043081</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G12" s="10">
         <v>1026310</v>
       </c>
       <c r="H12" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>286</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>287</v>
       </c>
       <c r="J12" s="12">
         <v>4</v>
@@ -4638,17 +4639,17 @@
       <c r="P12" s="13">
         <v>30</v>
       </c>
-      <c r="Q12" s="44" t="s">
+      <c r="Q12" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="R12" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="R12" s="15" t="s">
+      <c r="S12" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="S12" s="16" t="s">
+      <c r="T12" s="24" t="s">
         <v>290</v>
-      </c>
-      <c r="T12" s="24" t="s">
-        <v>291</v>
       </c>
       <c r="U12" s="24" t="s">
         <v>104</v>
@@ -4660,7 +4661,7 @@
         <v>106</v>
       </c>
       <c r="X12" s="25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Y12" s="26" t="s">
         <v>108</v>
@@ -4675,7 +4676,7 @@
         <v>110</v>
       </c>
       <c r="AC12" s="25" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AD12" s="26" t="s">
         <v>112</v>
@@ -4690,7 +4691,7 @@
         <v>2010</v>
       </c>
       <c r="AH12" s="19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AI12" s="19">
         <v>410</v>
@@ -4699,10 +4700,10 @@
         <v>375</v>
       </c>
       <c r="AK12" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AL12" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AM12" s="19">
         <v>520</v>
@@ -4711,22 +4712,22 @@
         <v>90</v>
       </c>
       <c r="AO12" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="AQ12" s="19" t="s">
         <v>296</v>
-      </c>
-      <c r="AP12" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="AQ12" s="19" t="s">
-        <v>297</v>
       </c>
       <c r="AR12" s="19" t="s">
         <v>156</v>
       </c>
       <c r="AS12" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="AT12" s="19" t="s">
         <v>298</v>
-      </c>
-      <c r="AT12" s="19" t="s">
-        <v>299</v>
       </c>
       <c r="AU12" s="19">
         <v>190</v>
@@ -4735,10 +4736,10 @@
         <v>24</v>
       </c>
       <c r="AW12" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AX12" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AY12" s="19">
         <v>180</v>
@@ -4779,38 +4780,38 @@
         <v>18</v>
       </c>
       <c r="BM12" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BN12" s="19" t="s">
         <v>123</v>
       </c>
       <c r="BO12" s="17" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="BP12" s="17" t="s">
         <v>125</v>
       </c>
       <c r="BQ12" s="16"/>
       <c r="BR12" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="BS12" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="BS12" s="22" t="s">
+      <c r="BT12" s="22" t="s">
         <v>303</v>
-      </c>
-      <c r="BT12" s="22" t="s">
-        <v>304</v>
       </c>
       <c r="BU12" s="22">
         <v>1466</v>
       </c>
       <c r="BV12" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="BW12" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="BW12" s="16" t="s">
-        <v>306</v>
-      </c>
       <c r="BX12" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BY12" s="16" t="s">
         <v>99</v>
@@ -4819,7 +4820,7 @@
         <v>99</v>
       </c>
       <c r="CA12" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="CB12" s="16" t="s">
         <v>125</v>
@@ -4831,16 +4832,16 @@
         <v>135</v>
       </c>
       <c r="CE12" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="CF12" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="CG12" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="CG12" s="16" t="s">
-        <v>310</v>
-      </c>
       <c r="CH12" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="CI12" s="16"/>
       <c r="CJ12" s="16"/>
@@ -4850,13 +4851,13 @@
     </row>
     <row r="13" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>311</v>
+      <c r="C13" s="41" t="s">
+        <v>310</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>93</v>
@@ -4871,10 +4872,10 @@
         <v>1024287</v>
       </c>
       <c r="H13" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="J13" s="12">
         <v>4</v>
@@ -4897,32 +4898,32 @@
       <c r="P13" s="13">
         <v>24</v>
       </c>
-      <c r="Q13" s="44" t="s">
-        <v>288</v>
+      <c r="Q13" s="43" t="s">
+        <v>287</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S13" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V13" s="17" t="s">
         <v>105</v>
       </c>
       <c r="W13" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="X13" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Y13" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Z13" s="17">
         <v>254</v>
@@ -4934,7 +4935,7 @@
         <v>110</v>
       </c>
       <c r="AC13" s="18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AD13" s="19" t="s">
         <v>112</v>
@@ -4949,7 +4950,7 @@
         <v>2055</v>
       </c>
       <c r="AH13" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AI13" s="19">
         <v>420</v>
@@ -4958,7 +4959,7 @@
         <v>385</v>
       </c>
       <c r="AK13" s="19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AL13" s="19" t="s">
         <v>115</v>
@@ -4982,10 +4983,10 @@
         <v>99</v>
       </c>
       <c r="AS13" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AT13" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AU13" s="19">
         <v>220</v>
@@ -4994,10 +4995,10 @@
         <v>27</v>
       </c>
       <c r="AW13" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AX13" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AY13" s="19">
         <v>210</v>
@@ -5038,47 +5039,47 @@
         <v>19</v>
       </c>
       <c r="BM13" s="19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BN13" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="BO13" s="17" t="s">
         <v>320</v>
-      </c>
-      <c r="BO13" s="17" t="s">
-        <v>321</v>
       </c>
       <c r="BP13" s="17" t="s">
         <v>125</v>
       </c>
       <c r="BQ13" s="16"/>
       <c r="BR13" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="BS13" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="BT13" s="22" t="s">
         <v>322</v>
-      </c>
-      <c r="BS13" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="BT13" s="22" t="s">
-        <v>323</v>
       </c>
       <c r="BU13" s="22">
         <v>1542</v>
       </c>
       <c r="BV13" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="BW13" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="BW13" s="16" t="s">
+      <c r="BX13" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="BY13" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ13" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="CA13" s="16" t="s">
         <v>325</v>
-      </c>
-      <c r="BX13" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="BY13" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="BZ13" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="CA13" s="16" t="s">
-        <v>326</v>
       </c>
       <c r="CB13" s="16" t="s">
         <v>125</v>
@@ -5087,19 +5088,19 @@
         <v>134</v>
       </c>
       <c r="CD13" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="CE13" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="CF13" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="CG13" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="CG13" s="16" t="s">
+      <c r="CH13" s="16" t="s">
         <v>328</v>
-      </c>
-      <c r="CH13" s="16" t="s">
-        <v>329</v>
       </c>
       <c r="CI13" s="16"/>
       <c r="CJ13" s="16"/>
@@ -5109,13 +5110,13 @@
     </row>
     <row r="14" spans="1:89" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>311</v>
+      <c r="C14" s="41" t="s">
+        <v>310</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>93</v>
@@ -5130,10 +5131,10 @@
         <v>1024287</v>
       </c>
       <c r="H14" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="J14" s="12">
         <v>4</v>
@@ -5156,32 +5157,32 @@
       <c r="P14" s="13">
         <v>24</v>
       </c>
-      <c r="Q14" s="44" t="s">
-        <v>288</v>
+      <c r="Q14" s="43" t="s">
+        <v>287</v>
       </c>
       <c r="R14" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S14" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="T14" s="24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="U14" s="24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V14" s="24" t="s">
         <v>105</v>
       </c>
       <c r="W14" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="X14" s="25" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Y14" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Z14" s="17">
         <v>254</v>
@@ -5193,7 +5194,7 @@
         <v>110</v>
       </c>
       <c r="AC14" s="25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AD14" s="26" t="s">
         <v>112</v>
@@ -5208,7 +5209,7 @@
         <v>2055</v>
       </c>
       <c r="AH14" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AI14" s="19">
         <v>420</v>
@@ -5217,7 +5218,7 @@
         <v>385</v>
       </c>
       <c r="AK14" s="19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AL14" s="19" t="s">
         <v>115</v>
@@ -5241,10 +5242,10 @@
         <v>99</v>
       </c>
       <c r="AS14" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AT14" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AU14" s="19">
         <v>220</v>
@@ -5253,10 +5254,10 @@
         <v>27</v>
       </c>
       <c r="AW14" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AX14" s="19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AY14" s="19">
         <v>210</v>
@@ -5297,47 +5298,47 @@
         <v>19</v>
       </c>
       <c r="BM14" s="19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BN14" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="BO14" s="17" t="s">
         <v>320</v>
-      </c>
-      <c r="BO14" s="17" t="s">
-        <v>321</v>
       </c>
       <c r="BP14" s="17" t="s">
         <v>125</v>
       </c>
       <c r="BQ14" s="16"/>
       <c r="BR14" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="BS14" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="BT14" s="22" t="s">
         <v>322</v>
-      </c>
-      <c r="BS14" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="BT14" s="22" t="s">
-        <v>323</v>
       </c>
       <c r="BU14" s="22">
         <v>1542</v>
       </c>
       <c r="BV14" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="BW14" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="BW14" s="16" t="s">
+      <c r="BX14" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="BY14" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="BZ14" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="CA14" s="16" t="s">
         <v>325</v>
-      </c>
-      <c r="BX14" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="BY14" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="BZ14" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="CA14" s="16" t="s">
-        <v>326</v>
       </c>
       <c r="CB14" s="16" t="s">
         <v>125</v>
@@ -5346,19 +5347,19 @@
         <v>134</v>
       </c>
       <c r="CD14" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="CE14" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="CF14" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="CG14" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="CG14" s="16" t="s">
+      <c r="CH14" s="16" t="s">
         <v>328</v>
-      </c>
-      <c r="CH14" s="16" t="s">
-        <v>329</v>
       </c>
       <c r="CI14" s="16"/>
       <c r="CJ14" s="16"/>
@@ -5367,7 +5368,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204724" right="0.1181102362204724" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="27" orientation="landscape" r:id="rId1"/>
